--- a/data/cronograma_goinfra_visual.xlsx
+++ b/data/cronograma_goinfra_visual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsulidario\Documents\VISUAL_SISTEMA\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F78949-0A8B-45EF-A620-D2D75051F06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA969EA6-6F79-48D5-BA9E-1110E6EA0BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{37BD73AA-4C49-4D7A-80D2-A80B90BE9793}"/>
   </bookViews>
@@ -485,11 +485,6 @@
     <t>206L5B041</t>
   </si>
   <si>
-    <t>Aguarda etapas montagem&gt; aferição
-Sem chuva até 04/03, Chuva forte a partir de 06/03.
-FALTA PLACA COMPOSTA E DE R19 - 80KM</t>
-  </si>
-  <si>
     <t>GO-206, KM 224,300, CAÇÚ</t>
   </si>
   <si>
@@ -2152,6 +2147,9 @@
   </si>
   <si>
     <t>SANTA FE DE GOIAS</t>
+  </si>
+  <si>
+    <t>Aguardando correção do relatório fotográfico - Falta R-19 depois 80 KM/H - R19 junto ao equipamento - composta terrestre</t>
   </si>
 </sst>
 </file>
@@ -2677,13 +2675,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -2695,79 +2693,79 @@
         <v>4</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="R1" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>0</v>
@@ -2776,37 +2774,37 @@
         <v>1</v>
       </c>
       <c r="AH1" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="AI1" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AQ1" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="AR1" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="2" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2927,10 +2925,10 @@
         <v>18</v>
       </c>
       <c r="AQ2" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="AR2" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="AR2" s="7" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="3" spans="1:44" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3053,10 +3051,10 @@
         <v>25</v>
       </c>
       <c r="AQ3" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="AR3" s="7" t="s">
         <v>628</v>
-      </c>
-      <c r="AR3" s="7" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3179,10 +3177,10 @@
         <v>30</v>
       </c>
       <c r="AQ4" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="AR4" s="7" t="s">
         <v>630</v>
-      </c>
-      <c r="AR4" s="7" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="5" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3287,10 +3285,10 @@
         <v>38</v>
       </c>
       <c r="AQ5" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="AR5" s="7" t="s">
         <v>634</v>
-      </c>
-      <c r="AR5" s="7" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -3395,10 +3393,10 @@
         <v>38</v>
       </c>
       <c r="AQ6" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="AR6" s="7" t="s">
         <v>634</v>
-      </c>
-      <c r="AR6" s="7" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="7" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -3521,10 +3519,10 @@
         <v>45</v>
       </c>
       <c r="AQ7" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="AR7" s="7" t="s">
         <v>638</v>
-      </c>
-      <c r="AR7" s="7" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -3647,10 +3645,10 @@
         <v>45</v>
       </c>
       <c r="AQ8" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="AR8" s="7" t="s">
         <v>638</v>
-      </c>
-      <c r="AR8" s="7" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -3773,10 +3771,10 @@
         <v>51</v>
       </c>
       <c r="AQ9" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="AR9" s="7" t="s">
         <v>686</v>
-      </c>
-      <c r="AR9" s="7" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -3899,10 +3897,10 @@
         <v>54</v>
       </c>
       <c r="AQ10" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="AR10" s="7" t="s">
         <v>688</v>
-      </c>
-      <c r="AR10" s="7" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="11" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -4025,10 +4023,10 @@
         <v>58</v>
       </c>
       <c r="AQ11" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="AR11" s="7" t="s">
         <v>690</v>
-      </c>
-      <c r="AR11" s="7" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -4151,10 +4149,10 @@
         <v>62</v>
       </c>
       <c r="AQ12" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="AR12" s="7" t="s">
         <v>564</v>
-      </c>
-      <c r="AR12" s="7" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="13" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -4277,10 +4275,10 @@
         <v>62</v>
       </c>
       <c r="AQ13" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="AR13" s="7" t="s">
         <v>564</v>
-      </c>
-      <c r="AR13" s="7" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="14" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -4397,10 +4395,10 @@
         <v>70</v>
       </c>
       <c r="AQ14" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="AR14" s="7" t="s">
         <v>632</v>
-      </c>
-      <c r="AR14" s="7" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -4517,10 +4515,10 @@
         <v>70</v>
       </c>
       <c r="AQ15" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="AR15" s="7" t="s">
         <v>632</v>
-      </c>
-      <c r="AR15" s="7" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -4643,10 +4641,10 @@
         <v>74</v>
       </c>
       <c r="AQ16" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="AR16" s="7" t="s">
         <v>642</v>
-      </c>
-      <c r="AR16" s="7" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="17" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -4769,10 +4767,10 @@
         <v>74</v>
       </c>
       <c r="AQ17" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="AR17" s="7" t="s">
         <v>642</v>
-      </c>
-      <c r="AR17" s="7" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="18" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -4895,10 +4893,10 @@
         <v>80</v>
       </c>
       <c r="AQ18" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="AR18" s="7" t="s">
         <v>644</v>
-      </c>
-      <c r="AR18" s="7" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="19" spans="1:44" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -5021,10 +5019,10 @@
         <v>80</v>
       </c>
       <c r="AQ19" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="AR19" s="7" t="s">
         <v>644</v>
-      </c>
-      <c r="AR19" s="7" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="20" spans="1:44" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5119,7 +5117,7 @@
       <c r="AK20" s="7"/>
       <c r="AL20" s="7"/>
       <c r="AM20" s="7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AN20" s="7" t="s">
         <v>76</v>
@@ -5131,10 +5129,10 @@
         <v>86</v>
       </c>
       <c r="AQ20" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="AR20" s="7" t="s">
         <v>646</v>
-      </c>
-      <c r="AR20" s="7" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="21" spans="1:44" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5235,7 +5233,7 @@
       <c r="AK21" s="7"/>
       <c r="AL21" s="7"/>
       <c r="AM21" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AN21" s="7" t="s">
         <v>76</v>
@@ -5247,10 +5245,10 @@
         <v>86</v>
       </c>
       <c r="AQ21" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="AR21" s="7" t="s">
         <v>646</v>
-      </c>
-      <c r="AR21" s="7" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="22" spans="1:44" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5361,10 +5359,10 @@
         <v>96</v>
       </c>
       <c r="AQ22" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="AR22" s="7" t="s">
         <v>648</v>
-      </c>
-      <c r="AR22" s="7" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="23" spans="1:44" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -5473,10 +5471,10 @@
         <v>96</v>
       </c>
       <c r="AQ23" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="AR23" s="7" t="s">
         <v>648</v>
-      </c>
-      <c r="AR23" s="7" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="24" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -5595,10 +5593,10 @@
         <v>101</v>
       </c>
       <c r="AQ24" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="AR24" s="7" t="s">
         <v>682</v>
-      </c>
-      <c r="AR24" s="7" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="25" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -5705,10 +5703,10 @@
         <v>105</v>
       </c>
       <c r="AQ25" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="AR25" s="7" t="s">
         <v>684</v>
-      </c>
-      <c r="AR25" s="7" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="26" spans="1:44" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5831,10 +5829,10 @@
         <v>109</v>
       </c>
       <c r="AQ26" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="AR26" s="7" t="s">
         <v>692</v>
-      </c>
-      <c r="AR26" s="7" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="27" spans="1:44" ht="218.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -5937,10 +5935,10 @@
         <v>116</v>
       </c>
       <c r="AQ27" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="AR27" s="7" t="s">
         <v>652</v>
-      </c>
-      <c r="AR27" s="7" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="28" spans="1:44" ht="218.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6043,10 +6041,10 @@
         <v>119</v>
       </c>
       <c r="AQ28" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="AR28" s="7" t="s">
         <v>654</v>
-      </c>
-      <c r="AR28" s="7" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="29" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
@@ -6143,7 +6141,7 @@
         <v>16</v>
       </c>
       <c r="AK29" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL29" s="7"/>
       <c r="AM29" s="7" t="s">
@@ -6159,10 +6157,10 @@
         <v>124</v>
       </c>
       <c r="AQ29" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="AR29" s="7" t="s">
         <v>656</v>
-      </c>
-      <c r="AR29" s="7" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="30" spans="1:44" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6269,10 +6267,10 @@
         <v>131</v>
       </c>
       <c r="AQ30" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="AR30" s="7" t="s">
         <v>666</v>
-      </c>
-      <c r="AR30" s="7" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="31" spans="1:44" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6379,10 +6377,10 @@
         <v>134</v>
       </c>
       <c r="AQ31" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="AR31" s="7" t="s">
         <v>668</v>
-      </c>
-      <c r="AR31" s="7" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="32" spans="1:44" ht="282" thickBot="1" x14ac:dyDescent="0.3">
@@ -6495,13 +6493,13 @@
         <v>143</v>
       </c>
       <c r="AQ32" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="AR32" s="7" t="s">
         <v>674</v>
       </c>
-      <c r="AR32" s="7" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="33" spans="1:44" ht="231" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:44" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>144</v>
       </c>
@@ -6575,7 +6573,9 @@
       <c r="AE33" s="12">
         <v>46094</v>
       </c>
-      <c r="AF33" s="7"/>
+      <c r="AF33" s="7" t="s">
+        <v>0</v>
+      </c>
       <c r="AG33" s="7" t="s">
         <v>14</v>
       </c>
@@ -6586,34 +6586,32 @@
         <v>15</v>
       </c>
       <c r="AJ33" s="7" t="s">
-        <v>139</v>
+        <v>16</v>
       </c>
       <c r="AK33" s="7"/>
       <c r="AL33" s="7" t="s">
         <v>93</v>
       </c>
       <c r="AM33" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="AN33" s="7" t="s">
-        <v>142</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="AN33" s="7"/>
       <c r="AO33" s="12">
         <v>46041</v>
       </c>
       <c r="AP33" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AQ33" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="AR33" s="7" t="s">
         <v>676</v>
-      </c>
-      <c r="AR33" s="7" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="34" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>8</v>
@@ -6628,10 +6626,10 @@
         <v>257.52499999999998</v>
       </c>
       <c r="F34" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>12</v>
@@ -6706,24 +6704,24 @@
       </c>
       <c r="AM34" s="7"/>
       <c r="AN34" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AO34" s="12">
         <v>46041</v>
       </c>
       <c r="AP34" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AQ34" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="AR34" s="7" t="s">
         <v>678</v>
-      </c>
-      <c r="AR34" s="7" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="35" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>8</v>
@@ -6738,10 +6736,10 @@
         <v>165.48</v>
       </c>
       <c r="F35" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>155</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>12</v>
@@ -6806,28 +6804,28 @@
       </c>
       <c r="AK35" s="7"/>
       <c r="AL35" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM35" s="7"/>
       <c r="AN35" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AO35" s="12">
         <v>46041</v>
       </c>
       <c r="AP35" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ35" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="AR35" s="7" t="s">
         <v>568</v>
-      </c>
-      <c r="AR35" s="7" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="36" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>8</v>
@@ -6842,10 +6840,10 @@
         <v>165.48</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>12</v>
@@ -6910,28 +6908,28 @@
       </c>
       <c r="AK36" s="7"/>
       <c r="AL36" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM36" s="7"/>
       <c r="AN36" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AO36" s="12">
         <v>46041</v>
       </c>
       <c r="AP36" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ36" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="AR36" s="7" t="s">
         <v>568</v>
-      </c>
-      <c r="AR36" s="7" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="37" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>8</v>
@@ -6946,10 +6944,10 @@
         <v>165.48</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>12</v>
@@ -7000,7 +6998,9 @@
       <c r="AD37" s="12">
         <v>46102</v>
       </c>
-      <c r="AE37" s="7"/>
+      <c r="AE37" s="12">
+        <v>46090</v>
+      </c>
       <c r="AF37" s="7"/>
       <c r="AG37" s="7" t="s">
         <v>36</v>
@@ -7012,32 +7012,32 @@
         <v>15</v>
       </c>
       <c r="AJ37" s="7" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="AK37" s="7"/>
       <c r="AL37" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM37" s="7"/>
       <c r="AN37" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AO37" s="12">
         <v>46041</v>
       </c>
       <c r="AP37" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ37" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="AR37" s="7" t="s">
         <v>568</v>
-      </c>
-      <c r="AR37" s="7" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="38" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>8</v>
@@ -7052,10 +7052,10 @@
         <v>165.48</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>12</v>
@@ -7106,7 +7106,9 @@
       <c r="AD38" s="12">
         <v>46102</v>
       </c>
-      <c r="AE38" s="7"/>
+      <c r="AE38" s="12">
+        <v>46090</v>
+      </c>
       <c r="AF38" s="7"/>
       <c r="AG38" s="7" t="s">
         <v>36</v>
@@ -7118,32 +7120,32 @@
         <v>15</v>
       </c>
       <c r="AJ38" s="7" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="AK38" s="7"/>
       <c r="AL38" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM38" s="7"/>
       <c r="AN38" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AO38" s="12">
         <v>46041</v>
       </c>
       <c r="AP38" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AQ38" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="AR38" s="7" t="s">
         <v>568</v>
-      </c>
-      <c r="AR38" s="7" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="39" spans="1:44" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>8</v>
@@ -7152,16 +7154,16 @@
         <v>46086</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39" s="7">
         <v>186.70099999999999</v>
       </c>
       <c r="F39" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G39" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>12</v>
@@ -7231,31 +7233,31 @@
         <v>91</v>
       </c>
       <c r="AK39" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL39" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="AL39" s="7" t="s">
+      <c r="AM39" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="AM39" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="AN39" s="7"/>
       <c r="AO39" s="12">
         <v>46041</v>
       </c>
       <c r="AP39" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AQ39" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="AR39" s="7" t="s">
         <v>580</v>
-      </c>
-      <c r="AR39" s="7" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="40" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>8</v>
@@ -7270,10 +7272,10 @@
         <v>432.83600000000001</v>
       </c>
       <c r="F40" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>12</v>
@@ -7352,18 +7354,18 @@
         <v>46042</v>
       </c>
       <c r="AP40" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AQ40" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="AR40" s="7" t="s">
         <v>680</v>
-      </c>
-      <c r="AR40" s="7" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="41" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>8</v>
@@ -7381,7 +7383,7 @@
         <v>33</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>12</v>
@@ -7467,27 +7469,27 @@
         <v>93</v>
       </c>
       <c r="AM41" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN41" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="AN41" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="AO41" s="12">
         <v>46042</v>
       </c>
       <c r="AP41" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AQ41" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="AR41" s="7" t="s">
         <v>636</v>
-      </c>
-      <c r="AR41" s="7" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="42" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>8</v>
@@ -7505,7 +7507,7 @@
         <v>33</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>12</v>
@@ -7591,27 +7593,27 @@
         <v>93</v>
       </c>
       <c r="AM42" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN42" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="AN42" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="AO42" s="12">
         <v>46042</v>
       </c>
       <c r="AP42" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AQ42" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="AR42" s="7" t="s">
         <v>636</v>
-      </c>
-      <c r="AR42" s="7" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="43" spans="1:44" ht="192.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>8</v>
@@ -7629,7 +7631,7 @@
         <v>42</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>12</v>
@@ -7701,7 +7703,7 @@
       <c r="AK43" s="7"/>
       <c r="AL43" s="7"/>
       <c r="AM43" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AN43" s="7" t="s">
         <v>44</v>
@@ -7710,18 +7712,18 @@
         <v>46042</v>
       </c>
       <c r="AP43" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AQ43" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="AR43" s="7" t="s">
         <v>640</v>
-      </c>
-      <c r="AR43" s="7" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="44" spans="1:44" ht="192.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>8</v>
@@ -7739,7 +7741,7 @@
         <v>42</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>12</v>
@@ -7811,27 +7813,27 @@
       <c r="AK44" s="7"/>
       <c r="AL44" s="7"/>
       <c r="AM44" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AN44" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AO44" s="12">
         <v>46042</v>
       </c>
       <c r="AP44" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AQ44" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="AR44" s="7" t="s">
         <v>640</v>
-      </c>
-      <c r="AR44" s="7" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="45" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>8</v>
@@ -7849,7 +7851,7 @@
         <v>21</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>12</v>
@@ -7923,31 +7925,31 @@
         <v>16</v>
       </c>
       <c r="AK45" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL45" s="7"/>
       <c r="AM45" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="AN45" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="AN45" s="7" t="s">
-        <v>189</v>
       </c>
       <c r="AO45" s="12">
         <v>46042</v>
       </c>
       <c r="AP45" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AQ45" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="AR45" s="7" t="s">
         <v>658</v>
-      </c>
-      <c r="AR45" s="7" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="46" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>8</v>
@@ -7965,7 +7967,7 @@
         <v>21</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>12</v>
@@ -8033,7 +8035,7 @@
         <v>67</v>
       </c>
       <c r="AK46" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL46" s="7" t="s">
         <v>68</v>
@@ -8044,18 +8046,18 @@
         <v>46042</v>
       </c>
       <c r="AP46" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AQ46" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="AR46" s="7" t="s">
         <v>660</v>
-      </c>
-      <c r="AR46" s="7" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="47" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>8</v>
@@ -8073,7 +8075,7 @@
         <v>21</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>12</v>
@@ -8141,7 +8143,7 @@
         <v>67</v>
       </c>
       <c r="AK47" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL47" s="7" t="s">
         <v>68</v>
@@ -8152,18 +8154,18 @@
         <v>46042</v>
       </c>
       <c r="AP47" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AQ47" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="AR47" s="7" t="s">
         <v>662</v>
-      </c>
-      <c r="AR47" s="7" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="48" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>8</v>
@@ -8181,7 +8183,7 @@
         <v>21</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>12</v>
@@ -8258,18 +8260,18 @@
         <v>46042</v>
       </c>
       <c r="AP48" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AQ48" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="AR48" s="7" t="s">
         <v>664</v>
-      </c>
-      <c r="AR48" s="7" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="49" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>8</v>
@@ -8287,7 +8289,7 @@
         <v>21</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>12</v>
@@ -8364,18 +8366,18 @@
         <v>46042</v>
       </c>
       <c r="AP49" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AQ49" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="AR49" s="7" t="s">
         <v>664</v>
-      </c>
-      <c r="AR49" s="7" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="50" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>8</v>
@@ -8393,7 +8395,7 @@
         <v>33</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>12</v>
@@ -8444,7 +8446,9 @@
       <c r="AD50" s="12">
         <v>46104</v>
       </c>
-      <c r="AE50" s="7"/>
+      <c r="AE50" s="12">
+        <v>46087</v>
+      </c>
       <c r="AF50" s="7"/>
       <c r="AG50" s="7" t="s">
         <v>36</v>
@@ -8456,7 +8460,7 @@
         <v>15</v>
       </c>
       <c r="AJ50" s="7" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="AK50" s="7"/>
       <c r="AL50" s="7" t="s">
@@ -8468,18 +8472,18 @@
         <v>46042</v>
       </c>
       <c r="AP50" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AQ50" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="AR50" s="7" t="s">
         <v>670</v>
-      </c>
-      <c r="AR50" s="7" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="51" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>8</v>
@@ -8497,7 +8501,7 @@
         <v>33</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>12</v>
@@ -8548,7 +8552,9 @@
       <c r="AD51" s="12">
         <v>46105</v>
       </c>
-      <c r="AE51" s="7"/>
+      <c r="AE51" s="12">
+        <v>46087</v>
+      </c>
       <c r="AF51" s="7"/>
       <c r="AG51" s="7" t="s">
         <v>36</v>
@@ -8560,7 +8566,7 @@
         <v>15</v>
       </c>
       <c r="AJ51" s="7" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="AK51" s="7"/>
       <c r="AL51" s="7" t="s">
@@ -8572,18 +8578,18 @@
         <v>46042</v>
       </c>
       <c r="AP51" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AQ51" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="AR51" s="7" t="s">
         <v>670</v>
-      </c>
-      <c r="AR51" s="7" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="52" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>8</v>
@@ -8601,7 +8607,7 @@
         <v>33</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>12</v>
@@ -8652,7 +8658,9 @@
       <c r="AD52" s="12">
         <v>46105</v>
       </c>
-      <c r="AE52" s="7"/>
+      <c r="AE52" s="12">
+        <v>46091</v>
+      </c>
       <c r="AF52" s="7"/>
       <c r="AG52" s="7" t="s">
         <v>36</v>
@@ -8664,7 +8672,7 @@
         <v>15</v>
       </c>
       <c r="AJ52" s="7" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="AK52" s="7"/>
       <c r="AL52" s="7" t="s">
@@ -8676,18 +8684,18 @@
         <v>46042</v>
       </c>
       <c r="AP52" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AQ52" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="AR52" s="7" t="s">
         <v>672</v>
-      </c>
-      <c r="AR52" s="7" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="53" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>8</v>
@@ -8705,7 +8713,7 @@
         <v>33</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>12</v>
@@ -8780,18 +8788,18 @@
         <v>46042</v>
       </c>
       <c r="AP53" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AQ53" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="AR53" s="7" t="s">
         <v>672</v>
-      </c>
-      <c r="AR53" s="7" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="54" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>8</v>
@@ -8809,7 +8817,7 @@
         <v>33</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>12</v>
@@ -8860,7 +8868,9 @@
       <c r="AD54" s="12">
         <v>46106</v>
       </c>
-      <c r="AE54" s="7"/>
+      <c r="AE54" s="12">
+        <v>46091</v>
+      </c>
       <c r="AF54" s="7"/>
       <c r="AG54" s="7" t="s">
         <v>36</v>
@@ -8872,7 +8882,7 @@
         <v>15</v>
       </c>
       <c r="AJ54" s="7" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="AK54" s="7"/>
       <c r="AL54" s="7" t="s">
@@ -8884,18 +8894,18 @@
         <v>46042</v>
       </c>
       <c r="AP54" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AQ54" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="AR54" s="7" t="s">
         <v>672</v>
-      </c>
-      <c r="AR54" s="7" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="55" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>8</v>
@@ -8913,7 +8923,7 @@
         <v>33</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>12</v>
@@ -8956,13 +8966,17 @@
       <c r="Z55" s="12">
         <v>46106</v>
       </c>
-      <c r="AA55" s="7"/>
+      <c r="AA55" s="12">
+        <v>46090</v>
+      </c>
       <c r="AB55" s="7"/>
       <c r="AC55" s="7"/>
       <c r="AD55" s="12">
         <v>46106</v>
       </c>
-      <c r="AE55" s="7"/>
+      <c r="AE55" s="12">
+        <v>46090</v>
+      </c>
       <c r="AF55" s="7"/>
       <c r="AG55" s="7" t="s">
         <v>36</v>
@@ -8974,7 +8988,7 @@
         <v>15</v>
       </c>
       <c r="AJ55" s="7" t="s">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="AK55" s="7"/>
       <c r="AL55" s="7" t="s">
@@ -8986,18 +9000,18 @@
         <v>46042</v>
       </c>
       <c r="AP55" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AQ55" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="AR55" s="7" t="s">
         <v>672</v>
-      </c>
-      <c r="AR55" s="7" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="56" spans="1:44" ht="409.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>8</v>
@@ -9015,7 +9029,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H56" s="7" t="s">
         <v>23</v>
@@ -9087,27 +9101,27 @@
       <c r="AK56" s="7"/>
       <c r="AL56" s="7"/>
       <c r="AM56" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="AN56" s="7" t="s">
         <v>213</v>
-      </c>
-      <c r="AN56" s="7" t="s">
-        <v>214</v>
       </c>
       <c r="AO56" s="12">
         <v>46042</v>
       </c>
       <c r="AP56" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AQ56" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="AR56" s="7" t="s">
         <v>562</v>
-      </c>
-      <c r="AR56" s="7" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="57" spans="1:44" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>8</v>
@@ -9122,10 +9136,10 @@
         <v>144.34100000000001</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>12</v>
@@ -9194,30 +9208,30 @@
       </c>
       <c r="AK57" s="7"/>
       <c r="AL57" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AM57" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AN57" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="AN57" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="AO57" s="12">
         <v>46042</v>
       </c>
       <c r="AP57" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AQ57" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="AR57" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="AR57" s="7" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="58" spans="1:44" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>8</v>
@@ -9232,10 +9246,10 @@
         <v>144.34100000000001</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>12</v>
@@ -9304,30 +9318,30 @@
       </c>
       <c r="AK58" s="7"/>
       <c r="AL58" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AM58" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AN58" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="AN58" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="AO58" s="12">
         <v>46042</v>
       </c>
       <c r="AP58" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AQ58" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="AR58" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="AR58" s="7" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="59" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>8</v>
@@ -9342,10 +9356,10 @@
         <v>166.501</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>12</v>
@@ -9416,28 +9430,28 @@
       </c>
       <c r="AK59" s="7"/>
       <c r="AL59" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM59" s="7"/>
       <c r="AN59" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AO59" s="12">
         <v>46042</v>
       </c>
       <c r="AP59" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AQ59" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="AR59" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="AR59" s="7" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="60" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>8</v>
@@ -9452,10 +9466,10 @@
         <v>166.501</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>12</v>
@@ -9526,28 +9540,28 @@
       </c>
       <c r="AK60" s="7"/>
       <c r="AL60" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM60" s="7"/>
       <c r="AN60" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AO60" s="12">
         <v>46042</v>
       </c>
       <c r="AP60" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AQ60" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="AR60" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="AR60" s="7" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="61" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>8</v>
@@ -9562,10 +9576,10 @@
         <v>170.46600000000001</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>12</v>
@@ -9632,28 +9646,28 @@
         <v>140</v>
       </c>
       <c r="AL61" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM61" s="7"/>
       <c r="AN61" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AO61" s="12">
         <v>46042</v>
       </c>
       <c r="AP61" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AQ61" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="AR61" s="7" t="s">
         <v>574</v>
-      </c>
-      <c r="AR61" s="7" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="62" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>8</v>
@@ -9668,10 +9682,10 @@
         <v>170.46600000000001</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>12</v>
@@ -9738,28 +9752,28 @@
         <v>140</v>
       </c>
       <c r="AL62" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM62" s="7"/>
       <c r="AN62" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AO62" s="12">
         <v>46042</v>
       </c>
       <c r="AP62" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AQ62" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="AR62" s="7" t="s">
         <v>574</v>
-      </c>
-      <c r="AR62" s="7" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="63" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>8</v>
@@ -9774,10 +9788,10 @@
         <v>200.935</v>
       </c>
       <c r="F63" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G63" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>12</v>
@@ -9847,23 +9861,23 @@
       </c>
       <c r="AL63" s="7"/>
       <c r="AM63" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="AN63" s="7" t="s">
         <v>234</v>
-      </c>
-      <c r="AN63" s="7" t="s">
-        <v>235</v>
       </c>
       <c r="AO63" s="12">
         <v>46042</v>
       </c>
       <c r="AP63" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AQ63" s="7"/>
       <c r="AR63" s="7"/>
     </row>
     <row r="64" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>8</v>
@@ -9878,10 +9892,10 @@
         <v>200.935</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>12</v>
@@ -9951,23 +9965,23 @@
       </c>
       <c r="AL64" s="7"/>
       <c r="AM64" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="AN64" s="7" t="s">
         <v>234</v>
-      </c>
-      <c r="AN64" s="7" t="s">
-        <v>235</v>
       </c>
       <c r="AO64" s="12">
         <v>46042</v>
       </c>
       <c r="AP64" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AQ64" s="7"/>
       <c r="AR64" s="7"/>
     </row>
     <row r="65" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>8</v>
@@ -9976,16 +9990,16 @@
         <v>46087</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E65" s="7">
         <v>159.96</v>
       </c>
       <c r="F65" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="G65" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>241</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>23</v>
@@ -10061,7 +10075,7 @@
         <v>68</v>
       </c>
       <c r="AM65" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN65" s="7" t="s">
         <v>115</v>
@@ -10070,18 +10084,18 @@
         <v>46042</v>
       </c>
       <c r="AP65" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AQ65" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="AR65" s="7" t="s">
         <v>592</v>
-      </c>
-      <c r="AR65" s="7" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="66" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>8</v>
@@ -10090,16 +10104,16 @@
         <v>46087</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E66" s="7">
         <v>159.572</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>23</v>
@@ -10171,7 +10185,7 @@
       <c r="AK66" s="7"/>
       <c r="AL66" s="7"/>
       <c r="AM66" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN66" s="7" t="s">
         <v>115</v>
@@ -10180,18 +10194,18 @@
         <v>46042</v>
       </c>
       <c r="AP66" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AQ66" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="AR66" s="7" t="s">
         <v>594</v>
-      </c>
-      <c r="AR66" s="7" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="67" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>8</v>
@@ -10200,16 +10214,16 @@
         <v>46087</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E67" s="7">
         <v>192.18899999999999</v>
       </c>
       <c r="F67" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="G67" s="7" t="s">
         <v>248</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>249</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>23</v>
@@ -10274,10 +10288,10 @@
       </c>
       <c r="AK67" s="7"/>
       <c r="AL67" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM67" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN67" s="7" t="s">
         <v>115</v>
@@ -10286,18 +10300,18 @@
         <v>46042</v>
       </c>
       <c r="AP67" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AQ67" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="AR67" s="7" t="s">
         <v>596</v>
-      </c>
-      <c r="AR67" s="7" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="68" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>8</v>
@@ -10306,16 +10320,16 @@
         <v>46087</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E68" s="7">
         <v>192.70400000000001</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>23</v>
@@ -10380,10 +10394,10 @@
       </c>
       <c r="AK68" s="7"/>
       <c r="AL68" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM68" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AN68" s="7" t="s">
         <v>115</v>
@@ -10392,18 +10406,18 @@
         <v>46042</v>
       </c>
       <c r="AP68" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AQ68" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="AR68" s="7" t="s">
         <v>598</v>
-      </c>
-      <c r="AR68" s="7" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="69" spans="1:44" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>8</v>
@@ -10418,10 +10432,10 @@
         <v>501.37799999999999</v>
       </c>
       <c r="F69" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G69" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>256</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>23</v>
@@ -10499,7 +10513,7 @@
         <v>68</v>
       </c>
       <c r="AM69" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN69" s="7" t="s">
         <v>115</v>
@@ -10508,18 +10522,18 @@
         <v>46042</v>
       </c>
       <c r="AP69" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AQ69" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="AR69" s="7" t="s">
         <v>602</v>
-      </c>
-      <c r="AR69" s="7" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="70" spans="1:44" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>8</v>
@@ -10534,10 +10548,10 @@
         <v>501.37799999999999</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>23</v>
@@ -10615,7 +10629,7 @@
         <v>68</v>
       </c>
       <c r="AM70" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN70" s="7" t="s">
         <v>115</v>
@@ -10624,18 +10638,18 @@
         <v>46042</v>
       </c>
       <c r="AP70" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AQ70" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="AR70" s="7" t="s">
         <v>602</v>
-      </c>
-      <c r="AR70" s="7" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="71" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>8</v>
@@ -10644,16 +10658,16 @@
         <v>46087</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E71" s="7">
         <v>151.60499999999999</v>
       </c>
       <c r="F71" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G71" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>264</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>23</v>
@@ -10718,30 +10732,30 @@
       </c>
       <c r="AK71" s="7"/>
       <c r="AL71" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM71" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="AN71" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="AN71" s="7" t="s">
-        <v>266</v>
       </c>
       <c r="AO71" s="12">
         <v>46042</v>
       </c>
       <c r="AP71" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AQ71" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="AR71" s="7" t="s">
         <v>608</v>
-      </c>
-      <c r="AR71" s="7" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="72" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>8</v>
@@ -10750,16 +10764,16 @@
         <v>46087</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E72" s="7">
         <v>151.60499999999999</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>23</v>
@@ -10824,30 +10838,30 @@
       </c>
       <c r="AK72" s="7"/>
       <c r="AL72" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM72" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="AN72" s="7" t="s">
         <v>265</v>
-      </c>
-      <c r="AN72" s="7" t="s">
-        <v>266</v>
       </c>
       <c r="AO72" s="12">
         <v>46042</v>
       </c>
       <c r="AP72" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AQ72" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="AR72" s="7" t="s">
         <v>608</v>
-      </c>
-      <c r="AR72" s="7" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="73" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>8</v>
@@ -10856,16 +10870,16 @@
         <v>46087</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E73" s="7">
         <v>318.18099999999998</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>12</v>
@@ -10935,10 +10949,10 @@
         <v>67</v>
       </c>
       <c r="AK73" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL73" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AL73" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AM73" s="7"/>
       <c r="AN73" s="7"/>
@@ -10946,18 +10960,18 @@
         <v>46042</v>
       </c>
       <c r="AP73" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AQ73" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="AR73" s="7" t="s">
         <v>616</v>
-      </c>
-      <c r="AR73" s="7" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="74" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>8</v>
@@ -10966,16 +10980,16 @@
         <v>46087</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E74" s="7">
         <v>318.28399999999999</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>12</v>
@@ -11045,10 +11059,10 @@
         <v>67</v>
       </c>
       <c r="AK74" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL74" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AL74" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AM74" s="7"/>
       <c r="AN74" s="7"/>
@@ -11056,18 +11070,18 @@
         <v>46042</v>
       </c>
       <c r="AP74" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AQ74" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="AR74" s="7" t="s">
         <v>618</v>
-      </c>
-      <c r="AR74" s="7" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="75" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>8</v>
@@ -11076,16 +11090,16 @@
         <v>46087</v>
       </c>
       <c r="D75" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="F75" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="G75" s="7" t="s">
         <v>279</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>280</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>12</v>
@@ -11154,7 +11168,7 @@
         <v>92</v>
       </c>
       <c r="AL75" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM75" s="7"/>
       <c r="AN75" s="7"/>
@@ -11162,7 +11176,7 @@
         <v>46042</v>
       </c>
       <c r="AP75" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AQ75" s="13">
         <v>-14.399526</v>
@@ -11173,7 +11187,7 @@
     </row>
     <row r="76" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>8</v>
@@ -11188,10 +11202,10 @@
         <v>254.524</v>
       </c>
       <c r="F76" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G76" s="7" t="s">
         <v>283</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>284</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>23</v>
@@ -11261,27 +11275,27 @@
       <c r="AK76" s="7"/>
       <c r="AL76" s="7"/>
       <c r="AM76" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN76" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="AN76" s="7" t="s">
-        <v>286</v>
       </c>
       <c r="AO76" s="12">
         <v>46043</v>
       </c>
       <c r="AP76" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AQ76" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="AR76" s="7" t="s">
         <v>650</v>
-      </c>
-      <c r="AR76" s="7" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="77" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>8</v>
@@ -11296,10 +11310,10 @@
         <v>254.524</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>23</v>
@@ -11371,27 +11385,27 @@
         <v>93</v>
       </c>
       <c r="AM77" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN77" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="AN77" s="7" t="s">
-        <v>286</v>
       </c>
       <c r="AO77" s="12">
         <v>46043</v>
       </c>
       <c r="AP77" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AQ77" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="AR77" s="7" t="s">
         <v>650</v>
-      </c>
-      <c r="AR77" s="7" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="78" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>8</v>
@@ -11406,10 +11420,10 @@
         <v>254.524</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>23</v>
@@ -11475,27 +11489,27 @@
         <v>93</v>
       </c>
       <c r="AM78" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN78" s="7" t="s">
         <v>285</v>
-      </c>
-      <c r="AN78" s="7" t="s">
-        <v>286</v>
       </c>
       <c r="AO78" s="12">
         <v>46043</v>
       </c>
       <c r="AP78" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AQ78" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="AR78" s="7" t="s">
         <v>650</v>
-      </c>
-      <c r="AR78" s="7" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="79" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>8</v>
@@ -11510,10 +11524,10 @@
         <v>166.49199999999999</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>12</v>
@@ -11582,7 +11596,7 @@
       </c>
       <c r="AK79" s="7"/>
       <c r="AL79" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AM79" s="7"/>
       <c r="AN79" s="7"/>
@@ -11590,18 +11604,18 @@
         <v>46043</v>
       </c>
       <c r="AP79" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AQ79" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="AR79" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="AR79" s="7" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="80" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>8</v>
@@ -11616,10 +11630,10 @@
         <v>166.49199999999999</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>12</v>
@@ -11686,7 +11700,7 @@
       </c>
       <c r="AK80" s="7"/>
       <c r="AL80" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM80" s="7"/>
       <c r="AN80" s="7"/>
@@ -11694,18 +11708,18 @@
         <v>46043</v>
       </c>
       <c r="AP80" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AQ80" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="AR80" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="AR80" s="7" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="81" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>8</v>
@@ -11720,10 +11734,10 @@
         <v>187.89</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>12</v>
@@ -11790,7 +11804,7 @@
         <v>140</v>
       </c>
       <c r="AL81" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM81" s="7"/>
       <c r="AN81" s="7"/>
@@ -11798,18 +11812,18 @@
         <v>46043</v>
       </c>
       <c r="AP81" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AQ81" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="AR81" s="7" t="s">
         <v>576</v>
-      </c>
-      <c r="AR81" s="7" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="82" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>8</v>
@@ -11824,10 +11838,10 @@
         <v>188.108</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>12</v>
@@ -11906,7 +11920,7 @@
         <v>140</v>
       </c>
       <c r="AL82" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AM82" s="7"/>
       <c r="AN82" s="7"/>
@@ -11914,18 +11928,18 @@
         <v>46043</v>
       </c>
       <c r="AP82" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AQ82" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="AR82" s="7" t="s">
         <v>578</v>
-      </c>
-      <c r="AR82" s="7" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="83" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>8</v>
@@ -11934,16 +11948,16 @@
         <v>46088</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E83" s="7">
         <v>186.79599999999999</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>12</v>
@@ -12017,10 +12031,10 @@
         <v>16</v>
       </c>
       <c r="AK83" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL83" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AL83" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AM83" s="7"/>
       <c r="AN83" s="7"/>
@@ -12028,18 +12042,18 @@
         <v>46043</v>
       </c>
       <c r="AP83" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AQ83" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="AR83" s="7" t="s">
         <v>582</v>
-      </c>
-      <c r="AR83" s="7" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="84" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>8</v>
@@ -12048,16 +12062,16 @@
         <v>46088</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E84" s="7">
         <v>190.863</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>12</v>
@@ -12127,10 +12141,10 @@
         <v>91</v>
       </c>
       <c r="AK84" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL84" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AL84" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AM84" s="7"/>
       <c r="AN84" s="7"/>
@@ -12138,18 +12152,18 @@
         <v>46043</v>
       </c>
       <c r="AP84" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AQ84" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="AR84" s="7" t="s">
         <v>584</v>
-      </c>
-      <c r="AR84" s="7" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="85" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>8</v>
@@ -12158,16 +12172,16 @@
         <v>46088</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E85" s="7">
         <v>190.947</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>12</v>
@@ -12237,10 +12251,10 @@
         <v>91</v>
       </c>
       <c r="AK85" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL85" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AL85" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AM85" s="7"/>
       <c r="AN85" s="7"/>
@@ -12248,18 +12262,18 @@
         <v>46043</v>
       </c>
       <c r="AP85" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AQ85" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="AR85" s="7" t="s">
         <v>586</v>
-      </c>
-      <c r="AR85" s="7" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="86" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>8</v>
@@ -12268,16 +12282,16 @@
         <v>46088</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E86" s="7">
         <v>349.24</v>
       </c>
       <c r="F86" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G86" s="7" t="s">
         <v>310</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>311</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>12</v>
@@ -12318,13 +12332,13 @@
       <c r="X86" s="7"/>
       <c r="Y86" s="7"/>
       <c r="Z86" s="12">
-        <v>46103</v>
+        <v>46105</v>
       </c>
       <c r="AA86" s="7"/>
       <c r="AB86" s="7"/>
       <c r="AC86" s="7"/>
       <c r="AD86" s="12">
-        <v>46103</v>
+        <v>46105</v>
       </c>
       <c r="AE86" s="7"/>
       <c r="AF86" s="7"/>
@@ -12341,10 +12355,10 @@
         <v>67</v>
       </c>
       <c r="AK86" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL86" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM86" s="7"/>
       <c r="AN86" s="7"/>
@@ -12352,18 +12366,18 @@
         <v>46043</v>
       </c>
       <c r="AP86" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AQ86" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="AR86" s="7" t="s">
         <v>588</v>
-      </c>
-      <c r="AR86" s="7" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="87" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>8</v>
@@ -12372,16 +12386,16 @@
         <v>46088</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E87" s="7">
         <v>364.916</v>
       </c>
       <c r="F87" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="G87" s="7" t="s">
         <v>314</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>315</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>12</v>
@@ -12432,7 +12446,7 @@
       <c r="AB87" s="7"/>
       <c r="AC87" s="7"/>
       <c r="AD87" s="12">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="AE87" s="7"/>
       <c r="AF87" s="7"/>
@@ -12449,10 +12463,10 @@
         <v>67</v>
       </c>
       <c r="AK87" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL87" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM87" s="7"/>
       <c r="AN87" s="7"/>
@@ -12460,14 +12474,14 @@
         <v>46043</v>
       </c>
       <c r="AP87" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AQ87" s="7"/>
       <c r="AR87" s="7"/>
     </row>
     <row r="88" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>8</v>
@@ -12476,16 +12490,16 @@
         <v>46088</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E88" s="7">
         <v>364.916</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>12</v>
@@ -12549,10 +12563,10 @@
         <v>67</v>
       </c>
       <c r="AK88" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL88" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM88" s="7"/>
       <c r="AN88" s="7"/>
@@ -12560,14 +12574,14 @@
         <v>46043</v>
       </c>
       <c r="AP88" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AQ88" s="7"/>
       <c r="AR88" s="7"/>
     </row>
     <row r="89" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>8</v>
@@ -12576,16 +12590,16 @@
         <v>46088</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E89" s="7">
         <v>145.66800000000001</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>23</v>
@@ -12668,18 +12682,18 @@
         <v>46043</v>
       </c>
       <c r="AP89" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AQ89" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="AR89" s="7" t="s">
         <v>590</v>
-      </c>
-      <c r="AR89" s="7" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="90" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>8</v>
@@ -12688,16 +12702,16 @@
         <v>46088</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E90" s="7">
         <v>145.66800000000001</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>23</v>
@@ -12778,18 +12792,18 @@
         <v>46043</v>
       </c>
       <c r="AP90" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AQ90" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="AR90" s="7" t="s">
         <v>590</v>
-      </c>
-      <c r="AR90" s="7" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="91" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>8</v>
@@ -12804,10 +12818,10 @@
         <v>492.226</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H91" s="7" t="s">
         <v>23</v>
@@ -12857,7 +12871,7 @@
         <v>0</v>
       </c>
       <c r="AI91" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ91" s="7" t="s">
         <v>67</v>
@@ -12874,18 +12888,18 @@
         <v>46043</v>
       </c>
       <c r="AP91" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AQ91" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="AR91" s="7" t="s">
         <v>600</v>
-      </c>
-      <c r="AR91" s="7" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="92" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>8</v>
@@ -12900,10 +12914,10 @@
         <v>690.32100000000003</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>23</v>
@@ -12972,7 +12986,7 @@
         <v>92</v>
       </c>
       <c r="AL92" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM92" s="7"/>
       <c r="AN92" s="7"/>
@@ -12980,18 +12994,18 @@
         <v>46043</v>
       </c>
       <c r="AP92" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AQ92" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="AR92" s="7" t="s">
         <v>604</v>
-      </c>
-      <c r="AR92" s="7" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="93" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>8</v>
@@ -13006,10 +13020,10 @@
         <v>690.351</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>23</v>
@@ -13078,7 +13092,7 @@
         <v>92</v>
       </c>
       <c r="AL93" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM93" s="7"/>
       <c r="AN93" s="7"/>
@@ -13086,18 +13100,18 @@
         <v>46043</v>
       </c>
       <c r="AP93" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AQ93" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="AR93" s="7" t="s">
         <v>606</v>
-      </c>
-      <c r="AR93" s="7" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="94" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>8</v>
@@ -13112,10 +13126,10 @@
         <v>749.15099999999995</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>12</v>
@@ -13184,7 +13198,7 @@
         <v>92</v>
       </c>
       <c r="AL94" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM94" s="7"/>
       <c r="AN94" s="7"/>
@@ -13192,14 +13206,14 @@
         <v>46043</v>
       </c>
       <c r="AP94" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AQ94" s="7"/>
       <c r="AR94" s="7"/>
     </row>
     <row r="95" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>8</v>
@@ -13214,10 +13228,10 @@
         <v>749.15099999999995</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>12</v>
@@ -13294,14 +13308,14 @@
         <v>46043</v>
       </c>
       <c r="AP95" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AQ95" s="7"/>
       <c r="AR95" s="7"/>
     </row>
     <row r="96" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>8</v>
@@ -13310,16 +13324,16 @@
         <v>46088</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E96" s="7">
         <v>311.91000000000003</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>12</v>
@@ -13395,10 +13409,10 @@
         <v>16</v>
       </c>
       <c r="AK96" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL96" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AL96" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AM96" s="7"/>
       <c r="AN96" s="7"/>
@@ -13406,18 +13420,18 @@
         <v>46043</v>
       </c>
       <c r="AP96" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AQ96" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="AR96" s="7" t="s">
         <v>610</v>
-      </c>
-      <c r="AR96" s="7" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="97" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>8</v>
@@ -13426,16 +13440,16 @@
         <v>46088</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E97" s="7">
         <v>334.50099999999998</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>12</v>
@@ -13522,7 +13536,7 @@
         <v>92</v>
       </c>
       <c r="AL97" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM97" s="7"/>
       <c r="AN97" s="7"/>
@@ -13530,18 +13544,18 @@
         <v>46043</v>
       </c>
       <c r="AP97" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AQ97" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="AR97" s="7" t="s">
         <v>620</v>
-      </c>
-      <c r="AR97" s="7" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="98" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>8</v>
@@ -13550,16 +13564,16 @@
         <v>46088</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E98" s="7">
         <v>334.50099999999998</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>12</v>
@@ -13646,7 +13660,7 @@
         <v>92</v>
       </c>
       <c r="AL98" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM98" s="7"/>
       <c r="AN98" s="7"/>
@@ -13654,18 +13668,18 @@
         <v>46043</v>
       </c>
       <c r="AP98" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AQ98" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="AR98" s="7" t="s">
         <v>620</v>
-      </c>
-      <c r="AR98" s="7" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="99" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>8</v>
@@ -13674,16 +13688,16 @@
         <v>46088</v>
       </c>
       <c r="D99" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F99" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="E99" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="F99" s="7" t="s">
+      <c r="G99" s="7" t="s">
         <v>346</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>347</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>12</v>
@@ -13754,7 +13768,7 @@
       </c>
       <c r="AK99" s="7"/>
       <c r="AL99" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM99" s="7"/>
       <c r="AN99" s="7"/>
@@ -13762,7 +13776,7 @@
         <v>46043</v>
       </c>
       <c r="AP99" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AQ99" s="13">
         <v>-13.890625999999999</v>
@@ -13773,7 +13787,7 @@
     </row>
     <row r="100" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>8</v>
@@ -13782,16 +13796,16 @@
         <v>46089</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E100" s="7">
         <v>311.25099999999998</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>12</v>
@@ -13867,10 +13881,10 @@
         <v>16</v>
       </c>
       <c r="AK100" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL100" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AL100" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AM100" s="7"/>
       <c r="AN100" s="7"/>
@@ -13878,18 +13892,18 @@
         <v>46044</v>
       </c>
       <c r="AP100" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AQ100" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="AR100" s="7" t="s">
         <v>612</v>
-      </c>
-      <c r="AR100" s="7" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="101" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>8</v>
@@ -13898,16 +13912,16 @@
         <v>46089</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E101" s="7">
         <v>314.69</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H101" s="7" t="s">
         <v>23</v>
@@ -13981,10 +13995,10 @@
         <v>16</v>
       </c>
       <c r="AK101" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL101" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AM101" s="7"/>
       <c r="AN101" s="7"/>
@@ -13992,18 +14006,18 @@
         <v>46044</v>
       </c>
       <c r="AP101" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AQ101" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="AR101" s="7" t="s">
         <v>614</v>
-      </c>
-      <c r="AR101" s="7" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="102" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>8</v>
@@ -14012,16 +14026,16 @@
         <v>46089</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E102" s="7">
         <v>314.69</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>23</v>
@@ -14093,10 +14107,10 @@
         <v>139</v>
       </c>
       <c r="AK102" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL102" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AM102" s="7"/>
       <c r="AN102" s="7"/>
@@ -14104,21 +14118,21 @@
         <v>46044</v>
       </c>
       <c r="AP102" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AQ102" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="AR102" s="7" t="s">
         <v>614</v>
-      </c>
-      <c r="AR102" s="7" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="103" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B103" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="C103" s="12">
         <v>46090</v>
@@ -14130,10 +14144,10 @@
         <v>761</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>12</v>
@@ -14208,21 +14222,21 @@
         <v>46045</v>
       </c>
       <c r="AP103" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AQ103" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="AR103" s="7" t="s">
         <v>622</v>
-      </c>
-      <c r="AR103" s="7" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="104" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B104" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="C104" s="12">
         <v>46090</v>
@@ -14234,10 +14248,10 @@
         <v>761</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>12</v>
@@ -14302,7 +14316,7 @@
       </c>
       <c r="AK104" s="7"/>
       <c r="AL104" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM104" s="7"/>
       <c r="AN104" s="7"/>
@@ -14310,21 +14324,21 @@
         <v>46045</v>
       </c>
       <c r="AP104" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AQ104" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="AR104" s="7" t="s">
         <v>622</v>
-      </c>
-      <c r="AR104" s="7" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="105" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C105" s="12">
         <v>46090</v>
@@ -14336,10 +14350,10 @@
         <v>555</v>
       </c>
       <c r="F105" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="G105" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="G105" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>23</v>
@@ -14412,21 +14426,21 @@
         <v>46045</v>
       </c>
       <c r="AP105" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AQ105" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="AR105" s="7" t="s">
         <v>624</v>
-      </c>
-      <c r="AR105" s="7" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="106" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C106" s="12">
         <v>46090</v>
@@ -14438,10 +14452,10 @@
         <v>555</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H106" s="7" t="s">
         <v>23</v>
@@ -14514,27 +14528,27 @@
         <v>46045</v>
       </c>
       <c r="AP106" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AQ106" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="AR106" s="7" t="s">
         <v>624</v>
-      </c>
-      <c r="AR106" s="7" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="107" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C107" s="12">
         <v>46103</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E107" s="7">
         <v>5.0000000000000001E-3</v>
@@ -14543,7 +14557,7 @@
         <v>21</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H107" s="7" t="s">
         <v>23</v>
@@ -14597,7 +14611,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ107" s="7" t="s">
         <v>67</v>
@@ -14612,7 +14626,7 @@
         <v>46058</v>
       </c>
       <c r="AP107" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AQ107" s="13">
         <v>-16.463206660000001</v>
@@ -14623,16 +14637,16 @@
     </row>
     <row r="108" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C108" s="12">
         <v>46103</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E108" s="7">
         <v>0</v>
@@ -14641,7 +14655,7 @@
         <v>21</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H108" s="7" t="s">
         <v>23</v>
@@ -14695,7 +14709,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ108" s="7" t="s">
         <v>67</v>
@@ -14710,7 +14724,7 @@
         <v>46058</v>
       </c>
       <c r="AP108" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AQ108" s="13">
         <v>-16.463207929999999</v>
@@ -14721,7 +14735,7 @@
     </row>
     <row r="109" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>8</v>
@@ -14736,10 +14750,10 @@
         <v>167.20500000000001</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H109" s="7" t="s">
         <v>12</v>
@@ -14802,7 +14816,7 @@
         <v>140</v>
       </c>
       <c r="AL109" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM109" s="7"/>
       <c r="AN109" s="7"/>
@@ -14810,18 +14824,18 @@
         <v>46072</v>
       </c>
       <c r="AP109" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AQ109" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="AR109" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="AR109" s="7" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="110" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>8</v>
@@ -14836,10 +14850,10 @@
         <v>167.20500000000001</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H110" s="7" t="s">
         <v>12</v>
@@ -14906,7 +14920,7 @@
         <v>140</v>
       </c>
       <c r="AL110" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM110" s="7"/>
       <c r="AN110" s="7"/>
@@ -14914,18 +14928,18 @@
         <v>46072</v>
       </c>
       <c r="AP110" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AQ110" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="AR110" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="AR110" s="7" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="111" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>8</v>
@@ -14940,10 +14954,10 @@
         <v>167.20500000000001</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H111" s="7" t="s">
         <v>12</v>
@@ -14997,7 +15011,7 @@
         <v>0</v>
       </c>
       <c r="AI111" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AJ111" s="7" t="s">
         <v>67</v>
@@ -15006,7 +15020,7 @@
         <v>140</v>
       </c>
       <c r="AL111" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AM111" s="7"/>
       <c r="AN111" s="7"/>
@@ -15014,18 +15028,18 @@
         <v>46072</v>
       </c>
       <c r="AP111" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AQ111" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="AR111" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="AR111" s="7" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="112" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>8</v>
@@ -15040,10 +15054,10 @@
         <v>167.20500000000001</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>12</v>
@@ -15110,7 +15124,7 @@
         <v>140</v>
       </c>
       <c r="AL112" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AM112" s="7"/>
       <c r="AN112" s="7"/>
@@ -15118,18 +15132,18 @@
         <v>46072</v>
       </c>
       <c r="AP112" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AQ112" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="AR112" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="AR112" s="7" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="113" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>8</v>
@@ -15138,16 +15152,16 @@
         <v>46117</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E113" s="7">
         <v>351.53300000000002</v>
       </c>
       <c r="F113" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G113" s="7" t="s">
         <v>381</v>
-      </c>
-      <c r="G113" s="7" t="s">
-        <v>382</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>12</v>
@@ -15192,13 +15206,13 @@
       <c r="X113" s="7"/>
       <c r="Y113" s="7"/>
       <c r="Z113" s="12">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AA113" s="7"/>
       <c r="AB113" s="7"/>
       <c r="AC113" s="7"/>
       <c r="AD113" s="12">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AE113" s="7"/>
       <c r="AF113" s="7"/>
@@ -15215,10 +15229,10 @@
         <v>67</v>
       </c>
       <c r="AK113" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL113" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM113" s="7"/>
       <c r="AN113" s="7"/>
@@ -15226,14 +15240,14 @@
         <v>46072</v>
       </c>
       <c r="AP113" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AQ113" s="7"/>
       <c r="AR113" s="7"/>
     </row>
     <row r="114" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>8</v>
@@ -15242,16 +15256,16 @@
         <v>46117</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E114" s="7">
         <v>351.53300000000002</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H114" s="7" t="s">
         <v>12</v>
@@ -15296,7 +15310,7 @@
       <c r="X114" s="7"/>
       <c r="Y114" s="7"/>
       <c r="Z114" s="12">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="AA114" s="7"/>
       <c r="AB114" s="7"/>
@@ -15319,10 +15333,10 @@
         <v>67</v>
       </c>
       <c r="AK114" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL114" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AM114" s="7"/>
       <c r="AN114" s="7"/>
@@ -15330,32 +15344,32 @@
         <v>46072</v>
       </c>
       <c r="AP114" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AQ114" s="7"/>
       <c r="AR114" s="7"/>
     </row>
     <row r="115" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B115" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>386</v>
       </c>
       <c r="C115" s="12">
         <v>46135</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E115" s="7">
         <v>280.05900000000003</v>
       </c>
       <c r="F115" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="G115" s="7" t="s">
         <v>387</v>
-      </c>
-      <c r="G115" s="7" t="s">
-        <v>388</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>12</v>
@@ -15393,7 +15407,7 @@
         <v>1</v>
       </c>
       <c r="AI115" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ115" s="7" t="s">
         <v>67</v>
@@ -15404,7 +15418,7 @@
       <c r="AN115" s="7"/>
       <c r="AO115" s="7"/>
       <c r="AP115" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AQ115" s="13">
         <v>-14.948444</v>
@@ -15415,25 +15429,25 @@
     </row>
     <row r="116" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B116" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>386</v>
       </c>
       <c r="C116" s="12">
         <v>46135</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E116" s="7">
         <v>280.05900000000003</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H116" s="7" t="s">
         <v>12</v>
@@ -15471,7 +15485,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ116" s="7" t="s">
         <v>67</v>
@@ -15482,7 +15496,7 @@
       <c r="AN116" s="7"/>
       <c r="AO116" s="7"/>
       <c r="AP116" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AQ116" s="13">
         <v>-14.948444</v>
@@ -15493,25 +15507,25 @@
     </row>
     <row r="117" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C117" s="12">
         <v>46136</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E117" s="7">
         <v>280.18200000000002</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>12</v>
@@ -15549,7 +15563,7 @@
         <v>1</v>
       </c>
       <c r="AI117" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ117" s="7" t="s">
         <v>67</v>
@@ -15560,7 +15574,7 @@
       <c r="AN117" s="7"/>
       <c r="AO117" s="7"/>
       <c r="AP117" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AQ117" s="13">
         <v>-14.947331999999999</v>
@@ -15571,25 +15585,25 @@
     </row>
     <row r="118" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C118" s="12">
         <v>46136</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E118" s="7">
         <v>280.18200000000002</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H118" s="7" t="s">
         <v>12</v>
@@ -15627,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="AI118" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ118" s="7" t="s">
         <v>67</v>
@@ -15638,7 +15652,7 @@
       <c r="AN118" s="7"/>
       <c r="AO118" s="7"/>
       <c r="AP118" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AQ118" s="13">
         <v>-14.947331999999999</v>
@@ -15649,10 +15663,10 @@
     </row>
     <row r="119" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C119" s="12">
         <v>46139</v>
@@ -15664,7 +15678,7 @@
         <v>261.33800000000002</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7" t="s">
@@ -15701,7 +15715,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ119" s="7" t="s">
         <v>67</v>
@@ -15712,7 +15726,7 @@
       <c r="AN119" s="7"/>
       <c r="AO119" s="7"/>
       <c r="AP119" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AQ119" s="13">
         <v>-16.301870000000001</v>
@@ -15723,10 +15737,10 @@
     </row>
     <row r="120" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C120" s="12">
         <v>46139</v>
@@ -15738,7 +15752,7 @@
         <v>261.33800000000002</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7" t="s">
@@ -15775,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="AI120" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ120" s="7" t="s">
         <v>67</v>
@@ -15786,7 +15800,7 @@
       <c r="AN120" s="7"/>
       <c r="AO120" s="7"/>
       <c r="AP120" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AQ120" s="13">
         <v>-16.301870000000001</v>
@@ -15797,20 +15811,20 @@
     </row>
     <row r="121" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C121" s="7"/>
       <c r="D121" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E121" s="7">
         <v>207.22</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7" t="s">
@@ -15847,7 +15861,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ121" s="7" t="s">
         <v>67</v>
@@ -15858,7 +15872,7 @@
       <c r="AN121" s="7"/>
       <c r="AO121" s="7"/>
       <c r="AP121" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AQ121" s="13">
         <v>-15.362679</v>
@@ -15869,20 +15883,20 @@
     </row>
     <row r="122" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C122" s="7"/>
       <c r="D122" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E122" s="7">
         <v>207.6</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="7" t="s">
@@ -15919,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AI122" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ122" s="7" t="s">
         <v>67</v>
@@ -15930,7 +15944,7 @@
       <c r="AN122" s="7"/>
       <c r="AO122" s="7"/>
       <c r="AP122" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AQ122" s="13">
         <v>-15.359247</v>
@@ -15941,20 +15955,20 @@
     </row>
     <row r="123" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C123" s="7"/>
       <c r="D123" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E123" s="7">
         <v>218.30500000000001</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="7" t="s">
@@ -15989,7 +16003,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ123" s="7" t="s">
         <v>67</v>
@@ -16000,7 +16014,7 @@
       <c r="AN123" s="7"/>
       <c r="AO123" s="7"/>
       <c r="AP123" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AQ123" s="13">
         <v>-15.33883</v>
@@ -16011,20 +16025,20 @@
     </row>
     <row r="124" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C124" s="7"/>
       <c r="D124" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E124" s="7">
         <v>218.30500000000001</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="7" t="s">
@@ -16059,7 +16073,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ124" s="7" t="s">
         <v>67</v>
@@ -16070,7 +16084,7 @@
       <c r="AN124" s="7"/>
       <c r="AO124" s="7"/>
       <c r="AP124" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AQ124" s="13">
         <v>-15.33883</v>
@@ -16081,20 +16095,20 @@
     </row>
     <row r="125" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C125" s="7"/>
       <c r="D125" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E125" s="7">
         <v>324.02199999999999</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="7" t="s">
@@ -16129,7 +16143,7 @@
         <v>0</v>
       </c>
       <c r="AI125" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ125" s="7" t="s">
         <v>67</v>
@@ -16140,7 +16154,7 @@
       <c r="AN125" s="7"/>
       <c r="AO125" s="7"/>
       <c r="AP125" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AQ125" s="13">
         <v>-14.579641000000001</v>
@@ -16151,20 +16165,20 @@
     </row>
     <row r="126" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C126" s="7"/>
       <c r="D126" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E126" s="7">
         <v>324.02199999999999</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7" t="s">
@@ -16199,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="AI126" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ126" s="7" t="s">
         <v>67</v>
@@ -16210,7 +16224,7 @@
       <c r="AN126" s="7"/>
       <c r="AO126" s="7"/>
       <c r="AP126" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AQ126" s="13">
         <v>-14.579641000000001</v>
@@ -16221,20 +16235,20 @@
     </row>
     <row r="127" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C127" s="7"/>
       <c r="D127" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E127" s="7">
         <v>58.094999999999999</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="7" t="s">
@@ -16269,7 +16283,7 @@
         <v>0</v>
       </c>
       <c r="AI127" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ127" s="7" t="s">
         <v>67</v>
@@ -16280,7 +16294,7 @@
       <c r="AN127" s="7"/>
       <c r="AO127" s="7"/>
       <c r="AP127" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AQ127" s="13">
         <v>-13.414666</v>
@@ -16291,20 +16305,20 @@
     </row>
     <row r="128" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C128" s="7"/>
       <c r="D128" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E128" s="7">
         <v>58.23</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7" t="s">
@@ -16339,7 +16353,7 @@
         <v>0</v>
       </c>
       <c r="AI128" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ128" s="7" t="s">
         <v>67</v>
@@ -16350,7 +16364,7 @@
       <c r="AN128" s="7"/>
       <c r="AO128" s="7"/>
       <c r="AP128" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AQ128" s="13">
         <v>-13.414799</v>
@@ -16361,20 +16375,20 @@
     </row>
     <row r="129" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C129" s="7"/>
       <c r="D129" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E129" s="7">
         <v>60.71</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7" t="s">
@@ -16409,7 +16423,7 @@
         <v>0</v>
       </c>
       <c r="AI129" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ129" s="7" t="s">
         <v>67</v>
@@ -16420,7 +16434,7 @@
       <c r="AN129" s="7"/>
       <c r="AO129" s="7"/>
       <c r="AP129" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AQ129" s="13">
         <v>-13.420337</v>
@@ -16431,20 +16445,20 @@
     </row>
     <row r="130" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C130" s="7"/>
       <c r="D130" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E130" s="7">
         <v>60.863</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="7" t="s">
@@ -16479,7 +16493,7 @@
         <v>0</v>
       </c>
       <c r="AI130" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ130" s="7" t="s">
         <v>67</v>
@@ -16490,7 +16504,7 @@
       <c r="AN130" s="7"/>
       <c r="AO130" s="7"/>
       <c r="AP130" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AQ130" s="13">
         <v>-13.420735000000001</v>
@@ -16501,20 +16515,20 @@
     </row>
     <row r="131" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C131" s="7"/>
       <c r="D131" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E131" s="7">
         <v>178.49</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="7" t="s">
@@ -16549,7 +16563,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ131" s="7" t="s">
         <v>67</v>
@@ -16560,7 +16574,7 @@
       <c r="AN131" s="7"/>
       <c r="AO131" s="7"/>
       <c r="AP131" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AQ131" s="13">
         <v>-13.267393</v>
@@ -16571,20 +16585,20 @@
     </row>
     <row r="132" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C132" s="7"/>
       <c r="D132" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E132" s="7">
         <v>178.43299999999999</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="7" t="s">
@@ -16619,7 +16633,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ132" s="7" t="s">
         <v>67</v>
@@ -16630,7 +16644,7 @@
       <c r="AN132" s="7"/>
       <c r="AO132" s="7"/>
       <c r="AP132" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AQ132" s="13">
         <v>-13.267295000000001</v>
@@ -16641,20 +16655,20 @@
     </row>
     <row r="133" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C133" s="7"/>
       <c r="D133" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E133" s="7">
         <v>54.712000000000003</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="7" t="s">
@@ -16689,7 +16703,7 @@
         <v>0</v>
       </c>
       <c r="AI133" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ133" s="7" t="s">
         <v>67</v>
@@ -16700,7 +16714,7 @@
       <c r="AN133" s="7"/>
       <c r="AO133" s="7"/>
       <c r="AP133" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AQ133" s="13">
         <v>-14.752395999999999</v>
@@ -16711,20 +16725,20 @@
     </row>
     <row r="134" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C134" s="7"/>
       <c r="D134" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E134" s="7">
         <v>54.712000000000003</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="7" t="s">
@@ -16759,7 +16773,7 @@
         <v>0</v>
       </c>
       <c r="AI134" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ134" s="7" t="s">
         <v>67</v>
@@ -16770,7 +16784,7 @@
       <c r="AN134" s="7"/>
       <c r="AO134" s="7"/>
       <c r="AP134" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AQ134" s="13">
         <v>-14.752395999999999</v>
@@ -16781,20 +16795,20 @@
     </row>
     <row r="135" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E135" s="7">
         <v>55.994999999999997</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="7" t="s">
@@ -16829,7 +16843,7 @@
         <v>0</v>
       </c>
       <c r="AI135" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ135" s="7" t="s">
         <v>67</v>
@@ -16840,7 +16854,7 @@
       <c r="AN135" s="7"/>
       <c r="AO135" s="7"/>
       <c r="AP135" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AQ135" s="13">
         <v>-14.756187000000001</v>
@@ -16851,20 +16865,20 @@
     </row>
     <row r="136" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C136" s="7"/>
       <c r="D136" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E136" s="7">
         <v>55.994999999999997</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7" t="s">
@@ -16899,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="AI136" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ136" s="7" t="s">
         <v>67</v>
@@ -16910,7 +16924,7 @@
       <c r="AN136" s="7"/>
       <c r="AO136" s="7"/>
       <c r="AP136" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AQ136" s="13">
         <v>-14.756187000000001</v>
@@ -16921,20 +16935,20 @@
     </row>
     <row r="137" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E137" s="7">
         <v>55.917000000000002</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7" t="s">
@@ -16969,7 +16983,7 @@
         <v>0</v>
       </c>
       <c r="AI137" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ137" s="7" t="s">
         <v>67</v>
@@ -16980,7 +16994,7 @@
       <c r="AN137" s="7"/>
       <c r="AO137" s="7"/>
       <c r="AP137" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ137" s="13">
         <v>-14.756099000000001</v>
@@ -16991,20 +17005,20 @@
     </row>
     <row r="138" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C138" s="7"/>
       <c r="D138" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E138" s="7">
         <v>55.917000000000002</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="7" t="s">
@@ -17039,7 +17053,7 @@
         <v>0</v>
       </c>
       <c r="AI138" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ138" s="7" t="s">
         <v>67</v>
@@ -17050,7 +17064,7 @@
       <c r="AN138" s="7"/>
       <c r="AO138" s="7"/>
       <c r="AP138" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AQ138" s="13">
         <v>-14.756099000000001</v>
@@ -17061,20 +17075,20 @@
     </row>
     <row r="139" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E139" s="7">
         <v>141.70099999999999</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="7" t="s">
@@ -17109,7 +17123,7 @@
         <v>0</v>
       </c>
       <c r="AI139" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ139" s="7" t="s">
         <v>67</v>
@@ -17120,7 +17134,7 @@
       <c r="AN139" s="7"/>
       <c r="AO139" s="7"/>
       <c r="AP139" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AQ139" s="13">
         <v>-14.529365</v>
@@ -17131,20 +17145,20 @@
     </row>
     <row r="140" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C140" s="7"/>
       <c r="D140" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E140" s="7">
         <v>141.73599999999999</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="7" t="s">
@@ -17179,7 +17193,7 @@
         <v>0</v>
       </c>
       <c r="AI140" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ140" s="7" t="s">
         <v>67</v>
@@ -17190,7 +17204,7 @@
       <c r="AN140" s="7"/>
       <c r="AO140" s="7"/>
       <c r="AP140" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AQ140" s="13">
         <v>-14.529325</v>
@@ -17201,14 +17215,14 @@
     </row>
     <row r="141" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E141" s="7">
         <v>58.158999999999999</v>
@@ -17249,7 +17263,7 @@
         <v>0</v>
       </c>
       <c r="AI141" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ141" s="7" t="s">
         <v>67</v>
@@ -17260,7 +17274,7 @@
       <c r="AN141" s="7"/>
       <c r="AO141" s="7"/>
       <c r="AP141" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AQ141" s="13">
         <v>-15.761200000000001</v>
@@ -17271,14 +17285,14 @@
     </row>
     <row r="142" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C142" s="7"/>
       <c r="D142" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E142" s="7">
         <v>58.142000000000003</v>
@@ -17319,7 +17333,7 @@
         <v>0</v>
       </c>
       <c r="AI142" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ142" s="7" t="s">
         <v>67</v>
@@ -17330,7 +17344,7 @@
       <c r="AN142" s="7"/>
       <c r="AO142" s="7"/>
       <c r="AP142" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AQ142" s="13">
         <v>-15.761240000000001</v>
@@ -17341,14 +17355,14 @@
     </row>
     <row r="143" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E143" s="7">
         <v>58.57</v>
@@ -17389,7 +17403,7 @@
         <v>0</v>
       </c>
       <c r="AI143" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ143" s="7" t="s">
         <v>67</v>
@@ -17400,7 +17414,7 @@
       <c r="AN143" s="7"/>
       <c r="AO143" s="7"/>
       <c r="AP143" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AQ143" s="13">
         <v>-15.761049999999999</v>
@@ -17411,14 +17425,14 @@
     </row>
     <row r="144" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C144" s="7"/>
       <c r="D144" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E144" s="7">
         <v>58.612000000000002</v>
@@ -17459,7 +17473,7 @@
         <v>0</v>
       </c>
       <c r="AI144" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ144" s="7" t="s">
         <v>67</v>
@@ -17470,7 +17484,7 @@
       <c r="AN144" s="7"/>
       <c r="AO144" s="7"/>
       <c r="AP144" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AQ144" s="13">
         <v>-15.761146</v>
@@ -17481,14 +17495,14 @@
     </row>
     <row r="145" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E145" s="7">
         <v>54.594999999999999</v>
@@ -17529,7 +17543,7 @@
         <v>0</v>
       </c>
       <c r="AI145" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ145" s="7" t="s">
         <v>67</v>
@@ -17540,7 +17554,7 @@
       <c r="AN145" s="7"/>
       <c r="AO145" s="7"/>
       <c r="AP145" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AQ145" s="13">
         <v>-15.743752000000001</v>
@@ -17551,14 +17565,14 @@
     </row>
     <row r="146" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C146" s="7"/>
       <c r="D146" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E146" s="7">
         <v>54.594999999999999</v>
@@ -17599,7 +17613,7 @@
         <v>0</v>
       </c>
       <c r="AI146" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ146" s="7" t="s">
         <v>67</v>
@@ -17610,7 +17624,7 @@
       <c r="AN146" s="7"/>
       <c r="AO146" s="7"/>
       <c r="AP146" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AQ146" s="13">
         <v>-15.743752000000001</v>
@@ -17621,20 +17635,20 @@
     </row>
     <row r="147" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E147" s="7">
         <v>356.59199999999998</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="7" t="s">
@@ -17669,7 +17683,7 @@
         <v>0</v>
       </c>
       <c r="AI147" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ147" s="7" t="s">
         <v>67</v>
@@ -17680,7 +17694,7 @@
       <c r="AN147" s="7"/>
       <c r="AO147" s="7"/>
       <c r="AP147" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AQ147" s="13">
         <v>-14.345764000000001</v>
@@ -17691,20 +17705,20 @@
     </row>
     <row r="148" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C148" s="7"/>
       <c r="D148" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E148" s="7">
         <v>356.59199999999998</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G148" s="7"/>
       <c r="H148" s="7" t="s">
@@ -17739,7 +17753,7 @@
         <v>0</v>
       </c>
       <c r="AI148" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ148" s="7" t="s">
         <v>67</v>
@@ -17750,7 +17764,7 @@
       <c r="AN148" s="7"/>
       <c r="AO148" s="7"/>
       <c r="AP148" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AQ148" s="13">
         <v>-14.345764000000001</v>
@@ -17761,20 +17775,20 @@
     </row>
     <row r="149" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E149" s="7">
         <v>307.01100000000002</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="7" t="s">
@@ -17809,7 +17823,7 @@
         <v>0</v>
       </c>
       <c r="AI149" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ149" s="7" t="s">
         <v>67</v>
@@ -17820,7 +17834,7 @@
       <c r="AN149" s="7"/>
       <c r="AO149" s="7"/>
       <c r="AP149" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AQ149" s="13">
         <v>-14.725806</v>
@@ -17831,20 +17845,20 @@
     </row>
     <row r="150" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C150" s="7"/>
       <c r="D150" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E150" s="7">
         <v>307.01100000000002</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="7" t="s">
@@ -17879,7 +17893,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ150" s="7" t="s">
         <v>67</v>
@@ -17890,7 +17904,7 @@
       <c r="AN150" s="7"/>
       <c r="AO150" s="7"/>
       <c r="AP150" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AQ150" s="13">
         <v>-14.725806</v>
@@ -17901,20 +17915,20 @@
     </row>
     <row r="151" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E151" s="7">
         <v>140.34</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G151" s="7"/>
       <c r="H151" s="7" t="s">
@@ -17949,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="AI151" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ151" s="7" t="s">
         <v>67</v>
@@ -17960,7 +17974,7 @@
       <c r="AN151" s="7"/>
       <c r="AO151" s="7"/>
       <c r="AP151" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AQ151" s="13">
         <v>-13.261065</v>
@@ -17971,20 +17985,20 @@
     </row>
     <row r="152" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C152" s="7"/>
       <c r="D152" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E152" s="7">
         <v>140.34</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G152" s="7"/>
       <c r="H152" s="7" t="s">
@@ -18019,7 +18033,7 @@
         <v>0</v>
       </c>
       <c r="AI152" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ152" s="7" t="s">
         <v>67</v>
@@ -18030,7 +18044,7 @@
       <c r="AN152" s="7"/>
       <c r="AO152" s="7"/>
       <c r="AP152" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AQ152" s="13">
         <v>-13.261065</v>
@@ -18041,20 +18055,20 @@
     </row>
     <row r="153" spans="1:44" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C153" s="7"/>
       <c r="D153" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E153" s="7">
         <v>239.417</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G153" s="7"/>
       <c r="H153" s="7" t="s">
@@ -18089,7 +18103,7 @@
         <v>0</v>
       </c>
       <c r="AI153" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ153" s="7" t="s">
         <v>67</v>
@@ -18100,7 +18114,7 @@
       <c r="AN153" s="7"/>
       <c r="AO153" s="7"/>
       <c r="AP153" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AQ153" s="13">
         <v>-14.190367999999999</v>
@@ -18111,10 +18125,10 @@
     </row>
     <row r="154" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C154" s="7"/>
       <c r="D154" s="7" t="s">
@@ -18124,7 +18138,7 @@
         <v>851.4</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G154" s="7"/>
       <c r="H154" s="7" t="s">
@@ -18161,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="AI154" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ154" s="7" t="s">
         <v>67</v>
@@ -18172,21 +18186,21 @@
       <c r="AN154" s="7"/>
       <c r="AO154" s="7"/>
       <c r="AP154" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AQ154" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="AR154" s="7" t="s">
         <v>626</v>
-      </c>
-      <c r="AR154" s="7" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="155" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7" t="s">
@@ -18196,7 +18210,7 @@
         <v>851.4</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G155" s="7"/>
       <c r="H155" s="7" t="s">
@@ -18233,7 +18247,7 @@
         <v>0</v>
       </c>
       <c r="AI155" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ155" s="7" t="s">
         <v>67</v>
@@ -18244,21 +18258,21 @@
       <c r="AN155" s="7"/>
       <c r="AO155" s="7"/>
       <c r="AP155" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AQ155" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="AR155" s="7" t="s">
         <v>626</v>
-      </c>
-      <c r="AR155" s="7" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="156" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C156" s="7"/>
       <c r="D156" s="7" t="s">
@@ -18268,7 +18282,7 @@
         <v>852.6</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G156" s="7"/>
       <c r="H156" s="7" t="s">
@@ -18305,7 +18319,7 @@
         <v>0</v>
       </c>
       <c r="AI156" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ156" s="7" t="s">
         <v>67</v>
@@ -18316,7 +18330,7 @@
       <c r="AN156" s="7"/>
       <c r="AO156" s="7"/>
       <c r="AP156" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AQ156" s="13">
         <v>-13.075587000000001</v>
@@ -18327,10 +18341,10 @@
     </row>
     <row r="157" spans="1:44" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C157" s="7"/>
       <c r="D157" s="7" t="s">
@@ -18340,7 +18354,7 @@
         <v>852.6</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G157" s="7"/>
       <c r="H157" s="7" t="s">
@@ -18377,7 +18391,7 @@
         <v>0</v>
       </c>
       <c r="AI157" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ157" s="7" t="s">
         <v>67</v>
@@ -18388,7 +18402,7 @@
       <c r="AN157" s="7"/>
       <c r="AO157" s="7"/>
       <c r="AP157" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AQ157" s="13">
         <v>-13.075587000000001</v>
@@ -18399,20 +18413,20 @@
     </row>
     <row r="158" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E158" s="7">
         <v>17.760000000000002</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G158" s="7"/>
       <c r="H158" s="7" t="s">
@@ -18447,7 +18461,7 @@
         <v>0</v>
       </c>
       <c r="AI158" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ158" s="7" t="s">
         <v>67</v>
@@ -18458,7 +18472,7 @@
       <c r="AN158" s="7"/>
       <c r="AO158" s="7"/>
       <c r="AP158" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AQ158" s="13">
         <v>-14.96654</v>
@@ -18469,20 +18483,20 @@
     </row>
     <row r="159" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C159" s="7"/>
       <c r="D159" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E159" s="7">
         <v>17.760000000000002</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G159" s="7"/>
       <c r="H159" s="7" t="s">
@@ -18517,7 +18531,7 @@
         <v>0</v>
       </c>
       <c r="AI159" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ159" s="7" t="s">
         <v>67</v>
@@ -18528,7 +18542,7 @@
       <c r="AN159" s="7"/>
       <c r="AO159" s="7"/>
       <c r="AP159" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AQ159" s="13">
         <v>-14.96654</v>
@@ -18539,20 +18553,20 @@
     </row>
     <row r="160" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C160" s="7"/>
       <c r="D160" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E160" s="7">
         <v>17.920000000000002</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G160" s="7"/>
       <c r="H160" s="7" t="s">
@@ -18587,7 +18601,7 @@
         <v>0</v>
       </c>
       <c r="AI160" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ160" s="7" t="s">
         <v>67</v>
@@ -18598,7 +18612,7 @@
       <c r="AN160" s="7"/>
       <c r="AO160" s="7"/>
       <c r="AP160" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AQ160" s="13">
         <v>-14.96654</v>
@@ -18609,20 +18623,20 @@
     </row>
     <row r="161" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E161" s="7">
         <v>17.920000000000002</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G161" s="7"/>
       <c r="H161" s="7" t="s">
@@ -18657,7 +18671,7 @@
         <v>0</v>
       </c>
       <c r="AI161" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ161" s="7" t="s">
         <v>67</v>
@@ -18668,7 +18682,7 @@
       <c r="AN161" s="7"/>
       <c r="AO161" s="7"/>
       <c r="AP161" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AQ161" s="13">
         <v>-14.96654</v>
@@ -18679,20 +18693,20 @@
     </row>
     <row r="162" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E162" s="7">
         <v>102.58</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G162" s="7"/>
       <c r="H162" s="7" t="s">
@@ -18727,7 +18741,7 @@
         <v>0</v>
       </c>
       <c r="AI162" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ162" s="7" t="s">
         <v>67</v>
@@ -18738,7 +18752,7 @@
       <c r="AN162" s="7"/>
       <c r="AO162" s="7"/>
       <c r="AP162" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AQ162" s="13">
         <v>-14.546315999999999</v>
@@ -18749,20 +18763,20 @@
     </row>
     <row r="163" spans="1:44" ht="167.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C163" s="7"/>
       <c r="D163" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E163" s="7">
         <v>94.15</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G163" s="7"/>
       <c r="H163" s="7" t="s">
@@ -18797,7 +18811,7 @@
         <v>0</v>
       </c>
       <c r="AI163" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ163" s="7" t="s">
         <v>67</v>
@@ -18806,11 +18820,11 @@
       <c r="AL163" s="7"/>
       <c r="AM163" s="7"/>
       <c r="AN163" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AO163" s="7"/>
       <c r="AP163" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AQ163" s="15">
         <v>-15775700</v>
@@ -18821,20 +18835,20 @@
     </row>
     <row r="164" spans="1:44" ht="167.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C164" s="7"/>
       <c r="D164" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E164" s="7">
         <v>94.15</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G164" s="7"/>
       <c r="H164" s="7" t="s">
@@ -18869,7 +18883,7 @@
         <v>0</v>
       </c>
       <c r="AI164" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ164" s="7" t="s">
         <v>67</v>
@@ -18878,11 +18892,11 @@
       <c r="AL164" s="7"/>
       <c r="AM164" s="7"/>
       <c r="AN164" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AO164" s="7"/>
       <c r="AP164" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AQ164" s="15">
         <v>-15775700</v>
@@ -18893,20 +18907,20 @@
     </row>
     <row r="165" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E165" s="7">
         <v>94.8</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G165" s="7"/>
       <c r="H165" s="7" t="s">
@@ -18941,7 +18955,7 @@
         <v>0</v>
       </c>
       <c r="AI165" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ165" s="7" t="s">
         <v>67</v>
@@ -18952,7 +18966,7 @@
       <c r="AN165" s="7"/>
       <c r="AO165" s="7"/>
       <c r="AP165" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AQ165" s="15">
         <v>-15775700</v>
@@ -18963,20 +18977,20 @@
     </row>
     <row r="166" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E166" s="7">
         <v>94.8</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G166" s="7"/>
       <c r="H166" s="7" t="s">
@@ -19011,7 +19025,7 @@
         <v>0</v>
       </c>
       <c r="AI166" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ166" s="7" t="s">
         <v>67</v>
@@ -19022,7 +19036,7 @@
       <c r="AN166" s="7"/>
       <c r="AO166" s="7"/>
       <c r="AP166" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AQ166" s="15">
         <v>-15775700</v>
@@ -19033,20 +19047,20 @@
     </row>
     <row r="167" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E167" s="7">
         <v>95.6</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G167" s="7"/>
       <c r="H167" s="7" t="s">
@@ -19081,7 +19095,7 @@
         <v>0</v>
       </c>
       <c r="AI167" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ167" s="7" t="s">
         <v>67</v>
@@ -19092,7 +19106,7 @@
       <c r="AN167" s="7"/>
       <c r="AO167" s="7"/>
       <c r="AP167" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AQ167" s="15">
         <v>-15775700</v>
@@ -19103,20 +19117,20 @@
     </row>
     <row r="168" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E168" s="7">
         <v>95.6</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G168" s="7"/>
       <c r="H168" s="7" t="s">
@@ -19151,7 +19165,7 @@
         <v>0</v>
       </c>
       <c r="AI168" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ168" s="7" t="s">
         <v>67</v>
@@ -19162,7 +19176,7 @@
       <c r="AN168" s="7"/>
       <c r="AO168" s="7"/>
       <c r="AP168" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AQ168" s="15">
         <v>-15775700</v>
@@ -19173,20 +19187,20 @@
     </row>
     <row r="169" spans="1:44" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E169" s="7">
         <v>127.45</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
@@ -19219,7 +19233,7 @@
         <v>0</v>
       </c>
       <c r="AI169" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ169" s="7" t="s">
         <v>67</v>
@@ -19228,11 +19242,11 @@
       <c r="AL169" s="7"/>
       <c r="AM169" s="7"/>
       <c r="AN169" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AO169" s="7"/>
       <c r="AP169" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AQ169" s="13">
         <v>-15.966638</v>
@@ -19243,20 +19257,20 @@
     </row>
     <row r="170" spans="1:44" ht="154.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E170" s="7">
         <v>127.45</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
@@ -19289,7 +19303,7 @@
         <v>0</v>
       </c>
       <c r="AI170" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ170" s="7" t="s">
         <v>67</v>
@@ -19298,11 +19312,11 @@
       <c r="AL170" s="7"/>
       <c r="AM170" s="7"/>
       <c r="AN170" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AO170" s="7"/>
       <c r="AP170" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AQ170" s="13">
         <v>-15.966638</v>
@@ -19313,20 +19327,20 @@
     </row>
     <row r="171" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E171" s="7">
         <v>529.79499999999996</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="7" t="s">
@@ -19361,7 +19375,7 @@
         <v>0</v>
       </c>
       <c r="AI171" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ171" s="7" t="s">
         <v>67</v>
@@ -19372,7 +19386,7 @@
       <c r="AN171" s="7"/>
       <c r="AO171" s="7"/>
       <c r="AP171" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AQ171" s="13">
         <v>-18.393274000000002</v>
@@ -19383,10 +19397,10 @@
     </row>
     <row r="172" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7" t="s">
@@ -19396,7 +19410,7 @@
         <v>262.86900000000003</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G172" s="7"/>
       <c r="H172" s="7" t="s">
@@ -19431,7 +19445,7 @@
         <v>0</v>
       </c>
       <c r="AI172" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ172" s="7" t="s">
         <v>67</v>
@@ -19442,7 +19456,7 @@
       <c r="AN172" s="7"/>
       <c r="AO172" s="7"/>
       <c r="AP172" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AQ172" s="13">
         <v>-16.308102000000002</v>
@@ -19453,10 +19467,10 @@
     </row>
     <row r="173" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7" t="s">
@@ -19466,7 +19480,7 @@
         <v>262.86900000000003</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G173" s="7"/>
       <c r="H173" s="7" t="s">
@@ -19501,7 +19515,7 @@
         <v>0</v>
       </c>
       <c r="AI173" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ173" s="7" t="s">
         <v>67</v>
@@ -19512,7 +19526,7 @@
       <c r="AN173" s="7"/>
       <c r="AO173" s="7"/>
       <c r="AP173" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AQ173" s="13">
         <v>-16.308102000000002</v>
@@ -19523,10 +19537,10 @@
     </row>
     <row r="174" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="7" t="s">
@@ -19536,7 +19550,7 @@
         <v>67.953999999999994</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7" t="s">
@@ -19571,7 +19585,7 @@
         <v>0</v>
       </c>
       <c r="AI174" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ174" s="7" t="s">
         <v>67</v>
@@ -19582,7 +19596,7 @@
       <c r="AN174" s="7"/>
       <c r="AO174" s="7"/>
       <c r="AP174" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AQ174" s="13">
         <v>-19.010909999999999</v>
@@ -19593,10 +19607,10 @@
     </row>
     <row r="175" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="7" t="s">
@@ -19606,7 +19620,7 @@
         <v>218.82400000000001</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G175" s="7"/>
       <c r="H175" s="7" t="s">
@@ -19641,7 +19655,7 @@
         <v>0</v>
       </c>
       <c r="AI175" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ175" s="7" t="s">
         <v>67</v>
@@ -19652,7 +19666,7 @@
       <c r="AN175" s="7"/>
       <c r="AO175" s="7"/>
       <c r="AP175" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AQ175" s="13">
         <v>-17.878209999999999</v>
@@ -19663,10 +19677,10 @@
     </row>
     <row r="176" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="7" t="s">
@@ -19676,7 +19690,7 @@
         <v>218.82400000000001</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="7" t="s">
@@ -19711,7 +19725,7 @@
         <v>0</v>
       </c>
       <c r="AI176" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ176" s="7" t="s">
         <v>67</v>
@@ -19722,7 +19736,7 @@
       <c r="AN176" s="7"/>
       <c r="AO176" s="7"/>
       <c r="AP176" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AQ176" s="13">
         <v>-17.878209999999999</v>
@@ -19733,10 +19747,10 @@
     </row>
     <row r="177" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="7" t="s">
@@ -19746,7 +19760,7 @@
         <v>285.03800000000001</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="7" t="s">
@@ -19781,7 +19795,7 @@
         <v>0</v>
       </c>
       <c r="AI177" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ177" s="7" t="s">
         <v>67</v>
@@ -19792,7 +19806,7 @@
       <c r="AN177" s="7"/>
       <c r="AO177" s="7"/>
       <c r="AP177" s="7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AQ177" s="13">
         <v>-17.446985000000002</v>
@@ -19803,10 +19817,10 @@
     </row>
     <row r="178" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="7" t="s">
@@ -19816,7 +19830,7 @@
         <v>285.31400000000002</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G178" s="7"/>
       <c r="H178" s="7" t="s">
@@ -19851,7 +19865,7 @@
         <v>0</v>
       </c>
       <c r="AI178" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ178" s="7" t="s">
         <v>67</v>
@@ -19862,7 +19876,7 @@
       <c r="AN178" s="7"/>
       <c r="AO178" s="7"/>
       <c r="AP178" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AQ178" s="13">
         <v>-17.444789</v>
@@ -19873,20 +19887,20 @@
     </row>
     <row r="179" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E179" s="7">
         <v>82.433999999999997</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G179" s="7"/>
       <c r="H179" s="7" t="s">
@@ -19921,7 +19935,7 @@
         <v>0</v>
       </c>
       <c r="AI179" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ179" s="7" t="s">
         <v>67</v>
@@ -19932,7 +19946,7 @@
       <c r="AN179" s="7"/>
       <c r="AO179" s="7"/>
       <c r="AP179" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AQ179" s="13">
         <v>-19.070689000000002</v>
@@ -19943,20 +19957,20 @@
     </row>
     <row r="180" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E180" s="7">
         <v>82.433999999999997</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G180" s="7"/>
       <c r="H180" s="7" t="s">
@@ -19991,7 +20005,7 @@
         <v>0</v>
       </c>
       <c r="AI180" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ180" s="7" t="s">
         <v>67</v>
@@ -20002,7 +20016,7 @@
       <c r="AN180" s="7"/>
       <c r="AO180" s="7"/>
       <c r="AP180" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AQ180" s="13">
         <v>-19.070689000000002</v>
@@ -20013,20 +20027,20 @@
     </row>
     <row r="181" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E181" s="7">
         <v>109.482</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G181" s="7"/>
       <c r="H181" s="7" t="s">
@@ -20061,7 +20075,7 @@
         <v>0</v>
       </c>
       <c r="AI181" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ181" s="7" t="s">
         <v>67</v>
@@ -20072,7 +20086,7 @@
       <c r="AN181" s="7"/>
       <c r="AO181" s="7"/>
       <c r="AP181" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AQ181" s="13">
         <v>-17.582388999999999</v>
@@ -20083,20 +20097,20 @@
     </row>
     <row r="182" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E182" s="7">
         <v>108.789</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7" t="s">
@@ -20131,7 +20145,7 @@
         <v>0</v>
       </c>
       <c r="AI182" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ182" s="7" t="s">
         <v>67</v>
@@ -20142,7 +20156,7 @@
       <c r="AN182" s="7"/>
       <c r="AO182" s="7"/>
       <c r="AP182" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AQ182" s="13">
         <v>-17.585239999999999</v>
@@ -20153,20 +20167,20 @@
     </row>
     <row r="183" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E183" s="7">
         <v>108.53700000000001</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G183" s="7"/>
       <c r="H183" s="7" t="s">
@@ -20201,7 +20215,7 @@
         <v>0</v>
       </c>
       <c r="AI183" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ183" s="7" t="s">
         <v>67</v>
@@ -20212,7 +20226,7 @@
       <c r="AN183" s="7"/>
       <c r="AO183" s="7"/>
       <c r="AP183" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AQ183" s="13">
         <v>-17.586549000000002</v>
@@ -20223,14 +20237,14 @@
     </row>
     <row r="184" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E184" s="7">
         <v>0.14699999999999999</v>
@@ -20271,7 +20285,7 @@
         <v>0</v>
       </c>
       <c r="AI184" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ184" s="7" t="s">
         <v>67</v>
@@ -20282,7 +20296,7 @@
       <c r="AN184" s="7"/>
       <c r="AO184" s="7"/>
       <c r="AP184" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AQ184" s="13">
         <v>-16.434301000000001</v>
@@ -20293,14 +20307,14 @@
     </row>
     <row r="185" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E185" s="7">
         <v>0.245</v>
@@ -20341,7 +20355,7 @@
         <v>0</v>
       </c>
       <c r="AI185" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ185" s="7" t="s">
         <v>67</v>
@@ -20352,7 +20366,7 @@
       <c r="AN185" s="7"/>
       <c r="AO185" s="7"/>
       <c r="AP185" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AQ185" s="13">
         <v>-16.435043</v>
@@ -20363,20 +20377,20 @@
     </row>
     <row r="186" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E186" s="7">
         <v>120.19</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G186" s="7"/>
       <c r="H186" s="7" t="s">
@@ -20411,7 +20425,7 @@
         <v>0</v>
       </c>
       <c r="AI186" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ186" s="7" t="s">
         <v>67</v>
@@ -20422,7 +20436,7 @@
       <c r="AN186" s="7"/>
       <c r="AO186" s="7"/>
       <c r="AP186" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AQ186" s="13">
         <v>-17.531146</v>
@@ -20433,20 +20447,20 @@
     </row>
     <row r="187" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E187" s="7">
         <v>120.19</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G187" s="7"/>
       <c r="H187" s="7" t="s">
@@ -20481,7 +20495,7 @@
         <v>0</v>
       </c>
       <c r="AI187" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ187" s="7" t="s">
         <v>67</v>
@@ -20492,7 +20506,7 @@
       <c r="AN187" s="7"/>
       <c r="AO187" s="7"/>
       <c r="AP187" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AQ187" s="13">
         <v>-17.531146</v>
@@ -20503,20 +20517,20 @@
     </row>
     <row r="188" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E188" s="7">
         <v>99.783000000000001</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G188" s="7"/>
       <c r="H188" s="7" t="s">
@@ -20551,7 +20565,7 @@
         <v>0</v>
       </c>
       <c r="AI188" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ188" s="7" t="s">
         <v>67</v>
@@ -20562,7 +20576,7 @@
       <c r="AN188" s="7"/>
       <c r="AO188" s="7"/>
       <c r="AP188" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AQ188" s="13">
         <v>-16.935421000000002</v>
@@ -20573,20 +20587,20 @@
     </row>
     <row r="189" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E189" s="7">
         <v>99.783000000000001</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G189" s="7"/>
       <c r="H189" s="7" t="s">
@@ -20621,7 +20635,7 @@
         <v>0</v>
       </c>
       <c r="AI189" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ189" s="7" t="s">
         <v>67</v>
@@ -20632,7 +20646,7 @@
       <c r="AN189" s="7"/>
       <c r="AO189" s="7"/>
       <c r="AP189" s="7" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AQ189" s="13">
         <v>-16.935421000000002</v>
@@ -20643,14 +20657,14 @@
     </row>
     <row r="190" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E190" s="7">
         <v>7.4089999999999998</v>
@@ -20691,7 +20705,7 @@
         <v>0</v>
       </c>
       <c r="AI190" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ190" s="7" t="s">
         <v>67</v>
@@ -20702,7 +20716,7 @@
       <c r="AN190" s="7"/>
       <c r="AO190" s="7"/>
       <c r="AP190" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AQ190" s="13">
         <v>-16.4983</v>
@@ -20713,14 +20727,14 @@
     </row>
     <row r="191" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E191" s="7">
         <v>7.4089999999999998</v>
@@ -20761,7 +20775,7 @@
         <v>0</v>
       </c>
       <c r="AI191" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ191" s="7" t="s">
         <v>67</v>
@@ -20772,7 +20786,7 @@
       <c r="AN191" s="7"/>
       <c r="AO191" s="7"/>
       <c r="AP191" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AQ191" s="13">
         <v>-16.4983</v>
@@ -20783,14 +20797,14 @@
     </row>
     <row r="192" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E192" s="7">
         <v>0.435</v>
@@ -20833,7 +20847,7 @@
         <v>0</v>
       </c>
       <c r="AI192" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ192" s="7" t="s">
         <v>67</v>
@@ -20844,7 +20858,7 @@
       <c r="AN192" s="7"/>
       <c r="AO192" s="7"/>
       <c r="AP192" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AQ192" s="13">
         <v>-16.436737000000001</v>
@@ -20855,10 +20869,10 @@
     </row>
     <row r="193" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="7" t="s">
@@ -20868,7 +20882,7 @@
         <v>279.60000000000002</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G193" s="7"/>
       <c r="H193" s="7" t="s">
@@ -20903,7 +20917,7 @@
         <v>0</v>
       </c>
       <c r="AI193" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ193" s="7" t="s">
         <v>67</v>
@@ -20914,17 +20928,17 @@
       <c r="AN193" s="7"/>
       <c r="AO193" s="7"/>
       <c r="AP193" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AQ193" s="7"/>
       <c r="AR193" s="7"/>
     </row>
     <row r="194" spans="1:44" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="7" t="s">
@@ -20934,7 +20948,7 @@
         <v>278.60000000000002</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G194" s="7"/>
       <c r="H194" s="7" t="s">
@@ -20969,7 +20983,7 @@
         <v>0</v>
       </c>
       <c r="AI194" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AJ194" s="7" t="s">
         <v>67</v>
@@ -20980,7 +20994,7 @@
       <c r="AN194" s="7"/>
       <c r="AO194" s="7"/>
       <c r="AP194" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AQ194" s="7"/>
       <c r="AR194" s="7"/>
